--- a/business_surveys/036_diversity_and_inclusion_report_form--business_surveys.xlsx
+++ b/business_surveys/036_diversity_and_inclusion_report_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'white_or_caucasian'}</t>
+          <t>white_or_caucasian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'White or Caucasian'}</t>
+          <t>White or Caucasian</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'hispanic_or_latino'}</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Hispanic or Latino'}</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'multiracial_or_multiracial'}</t>
+          <t>multiracial_or_multiracial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Multiracial or Multiracial'}</t>
+          <t>Multiracial or Multiracial</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'indigenous_or_native_american'}</t>
+          <t>indigenous_or_native_american</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Indigenous or Native American'}</t>
+          <t>Indigenous or Native American</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'middle_eastern_or_north_african'}</t>
+          <t>middle_eastern_or_north_african</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Middle Eastern or North African'}</t>
+          <t>Middle Eastern or North African</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flexible_work_hours'}</t>
+          <t>flexible_work_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flexible work hours'}</t>
+          <t>Flexible work hours</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'remote_work_options'}</t>
+          <t>remote_work_options</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Remote work options'}</t>
+          <t>Remote work options</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'diversity_and_inclusion_policies'}</t>
+          <t>diversity_and_inclusion_policies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Diversity and inclusion policies'}</t>
+          <t>Diversity and inclusion policies</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'employee_resource_groups'}</t>
+          <t>employee_resource_groups</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Employee resource groups'}</t>
+          <t>Employee resource groups</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'employee_resource_groups_for_people_of_color'}</t>
+          <t>employee_resource_groups_for_people_of_color</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Employee resource groups for people of color'}</t>
+          <t>Employee resource groups for people of color</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'employee_resource_groups_for_women'}</t>
+          <t>employee_resource_groups_for_women</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Employee resource groups for women'}</t>
+          <t>Employee resource groups for women</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'training_and_development_programs'}</t>
+          <t>training_and_development_programs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Training and development programs'}</t>
+          <t>Training and development programs</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'performance_management_and_promotion_practices'}</t>
+          <t>performance_management_and_promotion_practices</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Performance management and promotion practices'}</t>
+          <t>Performance management and promotion practices</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'microaggression'}</t>
+          <t>microaggression</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Microaggression'}</t>
+          <t>Microaggression</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inadequate_representation'}</t>
+          <t>inadequate_representation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inadequate representation'}</t>
+          <t>Inadequate representation</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'lack_of_support'}</t>
+          <t>lack_of_support</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Lack of support'}</t>
+          <t>Lack of support</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'exclusionary_practices'}</t>
+          <t>exclusionary_practices</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Exclusionary practices'}</t>
+          <t>Exclusionary practices</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'lack_of_accountability'}</t>
+          <t>lack_of_accountability</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Lack of accountability'}</t>
+          <t>Lack of accountability</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
